--- a/backend/data/uploads/MES/2026-07-19_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-19_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{857289FF-76A2-4B56-845D-F3C386893201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7BBCA8C-3214-47C9-AE2D-FDE3451E9DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{751B7100-4C48-4D5F-869A-1DA1E99BA923}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DAA39C75-BDAC-4214-BC9B-3D9DBF6A2026}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EB4B429-DF82-46DC-B46B-07EDDDE3289E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7969588A-34D4-41EE-8D28-FA3D7278AFA4}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-19_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-19_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F7BBCA8C-3214-47C9-AE2D-FDE3451E9DB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A51E845E-CD24-4FA8-ABFA-F0D732F6F44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{DAA39C75-BDAC-4214-BC9B-3D9DBF6A2026}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9B4E0929-B198-49A6-8A66-9771F5E88DDE}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7969588A-34D4-41EE-8D28-FA3D7278AFA4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B286DF-0BD4-4128-9051-C54CC302C017}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>

--- a/backend/data/uploads/MES/2026-07-19_불량현황.xlsx
+++ b/backend/data/uploads/MES/2026-07-19_불량현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sihoo\PythonProject\TestProject\backend\data\uploads\MES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A51E845E-CD24-4FA8-ABFA-F0D732F6F44D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76B221EB-709E-4825-97F7-C0DCDA2E6F56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{9B4E0929-B198-49A6-8A66-9771F5E88DDE}"/>
+    <workbookView xWindow="-30240" yWindow="8376" windowWidth="23040" windowHeight="12012" xr2:uid="{F2386793-49BD-4EE4-AF63-38A4D24E6950}"/>
   </bookViews>
   <sheets>
     <sheet name="불량현황" sheetId="1" r:id="rId1"/>
@@ -492,7 +492,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B286DF-0BD4-4128-9051-C54CC302C017}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{847BCCCC-EE17-4CA5-9579-49C5CE92ADBB}">
   <dimension ref="B2:U12"/>
   <sheetFormatPr defaultRowHeight="17.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
